--- a/artfynd/A 23192-2025 artfynd.xlsx
+++ b/artfynd/A 23192-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 23192-2025 artfynd.xlsx
+++ b/artfynd/A 23192-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 23192-2025 artfynd.xlsx
+++ b/artfynd/A 23192-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125201533</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 23192-2025 artfynd.xlsx
+++ b/artfynd/A 23192-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125201533</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
